--- a/train.xlsx
+++ b/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ChatbotPerpusBipa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{943D1B36-8D54-441A-800B-EFB0A24B0105}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675EE7B7-5582-4090-A7CB-DFC3811EAA46}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2752" uniqueCount="1377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="1253">
   <si>
     <t>text</t>
   </si>
@@ -3789,378 +3789,6 @@
   </si>
   <si>
     <t>Selamat sore, daftar peraturan yang tidak boleh dilanggar apa saja? Makasih</t>
-  </si>
-  <si>
-    <t>Apa aja yang bisa chatbot ini lakukan?</t>
-  </si>
-  <si>
-    <t>Fitur apa yang tersedia di chatbot ini?</t>
-  </si>
-  <si>
-    <t>Bisa bantu apa aja sih bot ini?</t>
-  </si>
-  <si>
-    <t>Kasih tahu dong daftar topik yang bisa ditanya</t>
-  </si>
-  <si>
-    <t>Command apa aja yang didukung?</t>
-  </si>
-  <si>
-    <t>Saya bisa tanya apa aja ke kamu?</t>
-  </si>
-  <si>
-    <t>Bisa list semua fitur kamu?</t>
-  </si>
-  <si>
-    <t>Hal apa saja yang bisa saya tanyakan di sini?</t>
-  </si>
-  <si>
-    <t>Daftar pertanyaan yang bisa diajukan apa aja?</t>
-  </si>
-  <si>
-    <t>Chatbot ini bisa bantu soal apa aja?</t>
-  </si>
-  <si>
-    <t>Ada panduan pakai chatbot ini gak?</t>
-  </si>
-  <si>
-    <t>Bisa sebutin semua fungsi kamu?</t>
-  </si>
-  <si>
-    <t>Apa perintah-perintah yang tersedia?</t>
-  </si>
-  <si>
-    <t>Tampilkan semua layanan kamu</t>
-  </si>
-  <si>
-    <t>Fiturnya ada apa aja ya?</t>
-  </si>
-  <si>
-    <t>Saya boleh tanya apa aja?</t>
-  </si>
-  <si>
-    <t>Bot ini bisa kasih informasi tentang apa aja?</t>
-  </si>
-  <si>
-    <t>Kasih tahu semua topik yang bisa dibahas</t>
-  </si>
-  <si>
-    <t>Kamu bisa bantu saya di topik apa aja?</t>
-  </si>
-  <si>
-    <t>Tampilkan menu utama chatbot ini dong</t>
-  </si>
-  <si>
-    <t>Menu perintah kamu apa aja?</t>
-  </si>
-  <si>
-    <t>Apa saja daftar intent di chatbot ini?</t>
-  </si>
-  <si>
-    <t>Saya baru pertama pakai, bisa minta daftar pertanyaan?</t>
-  </si>
-  <si>
-    <t>Chatbot ini cocok untuk nanya apa aja?</t>
-  </si>
-  <si>
-    <t>Arahkan saya ke daftar fitur kamu</t>
-  </si>
-  <si>
-    <t>Bisa tanya apa aja di chatbot ini?</t>
-  </si>
-  <si>
-    <t>Daftar pertanyaan yang bisa saya ajukan apa aja?</t>
-  </si>
-  <si>
-    <t>Apa aja fitur chatbotnya?</t>
-  </si>
-  <si>
-    <t>List perintah yang bisa digunakan dong</t>
-  </si>
-  <si>
-    <t>Command apa aja yang tersedia?</t>
-  </si>
-  <si>
-    <t>Tampilkan daftar topik yang bisa ditanya</t>
-  </si>
-  <si>
-    <t>Bisa bantu apa aja kamu?</t>
-  </si>
-  <si>
-    <t>Tolong spill menu pertanyaan yang didukung</t>
-  </si>
-  <si>
-    <t>Saya bisa nanya apa aja ke kamu?</t>
-  </si>
-  <si>
-    <t>Fitur-fitur kamu apa aja?</t>
-  </si>
-  <si>
-    <t>Ada daftar layanan yang bisa saya akses?</t>
-  </si>
-  <si>
-    <t>Perintah yang bisa diketik apa aja ya?</t>
-  </si>
-  <si>
-    <t>Menu utamanya apa aja?</t>
-  </si>
-  <si>
-    <t>Apa fungsi chatbot ini?</t>
-  </si>
-  <si>
-    <t>Topik apa aja yang bisa dibahas?</t>
-  </si>
-  <si>
-    <t>Ada template pertanyaan yang bisa saya ikuti?</t>
-  </si>
-  <si>
-    <t>List pertanyaan yang didukung tolong ditampilkan</t>
-  </si>
-  <si>
-    <t>Kamu bisa jawab soal apa aja?</t>
-  </si>
-  <si>
-    <t>Apa aja hal yang bisa saya minta lewat chatbot ini?</t>
-  </si>
-  <si>
-    <t>Bisa kasih tahu saya command list-nya?</t>
-  </si>
-  <si>
-    <t>Chatbot ini ngerti topik apa aja?</t>
-  </si>
-  <si>
-    <t>Ada help command gak?</t>
-  </si>
-  <si>
-    <t>Tolong tunjukkan fitur-fiturmu</t>
-  </si>
-  <si>
-    <t>Apa yang bisa kamu lakukan untuk saya?</t>
-  </si>
-  <si>
-    <t>Perintah bawaan kamu ada berapa?</t>
-  </si>
-  <si>
-    <t>Boleh minta daftar menu chatbot?</t>
-  </si>
-  <si>
-    <t>Tolong infokan daftar intent yang tersedia</t>
-  </si>
-  <si>
-    <t>Apa aja fungsi bot ini?</t>
-  </si>
-  <si>
-    <t>Kamu bisa bantu cari apa aja?</t>
-  </si>
-  <si>
-    <t>Cakupan chatbot ini seluas apa?</t>
-  </si>
-  <si>
-    <t>Kamu ngerti intent apa aja sih?</t>
-  </si>
-  <si>
-    <t>Tunjukkan semua fitur yang kamu punya</t>
-  </si>
-  <si>
-    <t>Saya baru pertama kali, bisa tanya soal apa aja?</t>
-  </si>
-  <si>
-    <t>Tampilkan semua kategori pertanyaan</t>
-  </si>
-  <si>
-    <t>Bisa bantu saya pakai daftar command?</t>
-  </si>
-  <si>
-    <t>Saya bingung, fitur yang bisa dipakai apa aja ya?</t>
-  </si>
-  <si>
-    <t>Tolong tampilkan semua jenis pertanyaan yang kamu pahami</t>
-  </si>
-  <si>
-    <t>Minta daftar keyword yang bisa dipakai</t>
-  </si>
-  <si>
-    <t>Bot ini bisa jawab soal apa?</t>
-  </si>
-  <si>
-    <t>Selamat pagi, saya baru di sini, bot ini bisa bantu apa aja ya?</t>
-  </si>
-  <si>
-    <t>Halo, fitur yang tersedia di chatbot ini apa aja?</t>
-  </si>
-  <si>
-    <t>Bot ini bisa ngapain aja sih?</t>
-  </si>
-  <si>
-    <t>Bisa bantu apa aja, bro?</t>
-  </si>
-  <si>
-    <t>Eh bot, kamu bisa jawab pertanyaan apa aja?</t>
-  </si>
-  <si>
-    <t>Saya bisa nanya apa aja di sini?</t>
-  </si>
-  <si>
-    <t>Menu chatbotnya apa aja nih?</t>
-  </si>
-  <si>
-    <t>Ini chatbot buat apa aja ya?</t>
-  </si>
-  <si>
-    <t>Daftar fitur kamu dong</t>
-  </si>
-  <si>
-    <t>Saya bingung, bisa bantu apa aja kamu?</t>
-  </si>
-  <si>
-    <t>Hai, saya baru pertama kali pakai, bisa tanya apa aja di sini?</t>
-  </si>
-  <si>
-    <t>Command apa aja yang bisa dipakai?</t>
-  </si>
-  <si>
-    <t>Show me all available commands</t>
-  </si>
-  <si>
-    <t>Bisa kasih daftar perintah yang bisa dipakai?</t>
-  </si>
-  <si>
-    <t>Bisa tanya apa aja ke kamu, bot?</t>
-  </si>
-  <si>
-    <t>Topik yang bisa dibahas di chatbot ini apa aja ya?</t>
-  </si>
-  <si>
-    <t>Apa aja yang bisa saya tanyakan lewat chat ini?</t>
-  </si>
-  <si>
-    <t>Daftar pertanyaan yang bisa diajukan dong</t>
-  </si>
-  <si>
-    <t>Bot ini kerjanya di bidang apa aja?</t>
-  </si>
-  <si>
-    <t>Coba spill fitur kamu dong</t>
-  </si>
-  <si>
-    <t>Ada menu utama gak?</t>
-  </si>
-  <si>
-    <t>Aku pengen tahu kamu bisa bantu di bidang apa aja</t>
-  </si>
-  <si>
-    <t>Bisa list semua fungsi kamu?</t>
-  </si>
-  <si>
-    <t>Tunjukin semua layanan chatbot ini dong</t>
-  </si>
-  <si>
-    <t>Fitur utama kamu apa aja?</t>
-  </si>
-  <si>
-    <t>Ini chatbot bisa bantu cari info apa aja?</t>
-  </si>
-  <si>
-    <t>Boleh minta daftar layanan kamu?</t>
-  </si>
-  <si>
-    <t>Bantu saya dong, saya bisa nanya apa aja?</t>
-  </si>
-  <si>
-    <t>Ini bisa buat tanya soal buku aja atau ada yang lain?</t>
-  </si>
-  <si>
-    <t>Gimana cara pakainya? Bisa tanya apa aja kah?</t>
-  </si>
-  <si>
-    <t>Semua fitur chatbot ini bisa dilihat di mana?</t>
-  </si>
-  <si>
-    <t>Hey bot, kasih tahu command yang bisa kupakai</t>
-  </si>
-  <si>
-    <t>Kasih tahu dong fitur yang bisa dipakai</t>
-  </si>
-  <si>
-    <t>Ada panduan fitur gak?</t>
-  </si>
-  <si>
-    <t>Bisa tolong kasih tahu layanan yang tersedia?</t>
-  </si>
-  <si>
-    <t>Show me what you can do</t>
-  </si>
-  <si>
-    <t>Saya baru daftar, boleh minta info fitur chatbotnya?</t>
-  </si>
-  <si>
-    <t>Oi, fitur lo apa aja?</t>
-  </si>
-  <si>
-    <t>Ini bisa dipakai buat apa aja ya?</t>
-  </si>
-  <si>
-    <t>Gue baru masuk nih, lo bisa bantu apa aja bro?</t>
-  </si>
-  <si>
-    <t>Tolong tunjukin daftar semua topik yang bisa gue tanya</t>
-  </si>
-  <si>
-    <t>Bot ini bantuin cari buku doang atau ada fitur lain?</t>
-  </si>
-  <si>
-    <t>Saya pengen tahu fitur-fitur yang bisa dipakai</t>
-  </si>
-  <si>
-    <t>Daftar lengkap pertanyaan yang bisa saya ajukan?</t>
-  </si>
-  <si>
-    <t>Jelaskan fungsi-fungsi chatbot ini dong</t>
-  </si>
-  <si>
-    <t>Semua intent yang tersedia apa aja ya?</t>
-  </si>
-  <si>
-    <t>Ada fitur khusus yang belum saya tahu?</t>
-  </si>
-  <si>
-    <t>Apa saja jenis bantuan yang bisa kamu kasih?</t>
-  </si>
-  <si>
-    <t>Jelasin dong semua hal yang bisa saya eksplor lewat chatbot ini</t>
-  </si>
-  <si>
-    <t>selamat malam, saya baru, apa aja yang ada disini?</t>
-  </si>
-  <si>
-    <t>test, cek command</t>
-  </si>
-  <si>
-    <t>command list</t>
-  </si>
-  <si>
-    <t>daftar command</t>
-  </si>
-  <si>
-    <t>daftar pertanyaan</t>
-  </si>
-  <si>
-    <t>daftar intent</t>
-  </si>
-  <si>
-    <t>cek daftar intent</t>
-  </si>
-  <si>
-    <t>list semua intent</t>
-  </si>
-  <si>
-    <t>apa saja pertanyaan</t>
-  </si>
-  <si>
-    <t>liat semua daftar topik</t>
-  </si>
-  <si>
-    <t>command</t>
   </si>
 </sst>
 </file>
@@ -5007,7 +4635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1376"/>
+  <dimension ref="A1:C1251"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100.28515625" bestFit="1" customWidth="1"/>
@@ -15030,1006 +14658,6 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="1252" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1252" t="s">
-        <v>1263</v>
-      </c>
-      <c r="B1252" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1253" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1253" t="s">
-        <v>1253</v>
-      </c>
-      <c r="B1253" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1254" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1254" t="s">
-        <v>1265</v>
-      </c>
-      <c r="B1254" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1255" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1255" t="s">
-        <v>1274</v>
-      </c>
-      <c r="B1255" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1256" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1256" t="s">
-        <v>1277</v>
-      </c>
-      <c r="B1256" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1257" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1257" t="s">
-        <v>1255</v>
-      </c>
-      <c r="B1257" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1258" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1258" t="s">
-        <v>1259</v>
-      </c>
-      <c r="B1258" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1259" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1259" t="s">
-        <v>1264</v>
-      </c>
-      <c r="B1259" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1260" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1260" t="s">
-        <v>1269</v>
-      </c>
-      <c r="B1260" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1261" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1261" t="s">
-        <v>1262</v>
-      </c>
-      <c r="B1261" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1262" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1262" t="s">
-        <v>1276</v>
-      </c>
-      <c r="B1262" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1263" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1263" t="s">
-        <v>1257</v>
-      </c>
-      <c r="B1263" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1264" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1264" t="s">
-        <v>1261</v>
-      </c>
-      <c r="B1264" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1265" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1265" t="s">
-        <v>1254</v>
-      </c>
-      <c r="B1265" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1266" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1266" t="s">
-        <v>1267</v>
-      </c>
-      <c r="B1266" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1267" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1267" t="s">
-        <v>1260</v>
-      </c>
-      <c r="B1267" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1268" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1268" t="s">
-        <v>1271</v>
-      </c>
-      <c r="B1268" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1269" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1269" t="s">
-        <v>1256</v>
-      </c>
-      <c r="B1269" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1270" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1270" t="s">
-        <v>1270</v>
-      </c>
-      <c r="B1270" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1271" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1271" t="s">
-        <v>1273</v>
-      </c>
-      <c r="B1271" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1272" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1272" t="s">
-        <v>1275</v>
-      </c>
-      <c r="B1272" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1273" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1273" t="s">
-        <v>1258</v>
-      </c>
-      <c r="B1273" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1274" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1274" t="s">
-        <v>1268</v>
-      </c>
-      <c r="B1274" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1275" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1275" t="s">
-        <v>1272</v>
-      </c>
-      <c r="B1275" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1276" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1276" t="s">
-        <v>1266</v>
-      </c>
-      <c r="B1276" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1277" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1277" t="s">
-        <v>1288</v>
-      </c>
-      <c r="B1277" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1278" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1278" t="s">
-        <v>1299</v>
-      </c>
-      <c r="B1278" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1279" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1279" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B1279" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1280" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1280" t="s">
-        <v>1280</v>
-      </c>
-      <c r="B1280" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1281" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1281" t="s">
-        <v>1305</v>
-      </c>
-      <c r="B1281" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1282" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1282" t="s">
-        <v>1296</v>
-      </c>
-      <c r="B1282" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1283" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1283" t="s">
-        <v>1291</v>
-      </c>
-      <c r="B1283" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1284" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1284" t="s">
-        <v>1301</v>
-      </c>
-      <c r="B1284" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1285" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1285" t="s">
-        <v>1284</v>
-      </c>
-      <c r="B1285" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1286" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1286" t="s">
-        <v>1312</v>
-      </c>
-      <c r="B1286" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1287" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1287" t="s">
-        <v>1297</v>
-      </c>
-      <c r="B1287" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1288" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1288" t="s">
-        <v>1278</v>
-      </c>
-      <c r="B1288" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1289" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1289" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B1289" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1290" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1290" t="s">
-        <v>1316</v>
-      </c>
-      <c r="B1290" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1291" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1291" t="s">
-        <v>1307</v>
-      </c>
-      <c r="B1291" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1292" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1292" t="s">
-        <v>1262</v>
-      </c>
-      <c r="B1292" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1293" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1293" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B1293" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1294" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1294" t="s">
-        <v>1282</v>
-      </c>
-      <c r="B1294" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1295" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1295" t="s">
-        <v>1279</v>
-      </c>
-      <c r="B1295" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1296" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1296" t="s">
-        <v>1287</v>
-      </c>
-      <c r="B1296" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1297" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1297" t="s">
-        <v>1306</v>
-      </c>
-      <c r="B1297" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1298" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1298" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B1298" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1299" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1299" t="s">
-        <v>1308</v>
-      </c>
-      <c r="B1299" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1300" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1300" t="s">
-        <v>1281</v>
-      </c>
-      <c r="B1300" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1301" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1301" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B1301" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1302" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1302" t="s">
-        <v>1290</v>
-      </c>
-      <c r="B1302" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1303" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1303" t="s">
-        <v>1315</v>
-      </c>
-      <c r="B1303" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1304" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1304" t="s">
-        <v>1302</v>
-      </c>
-      <c r="B1304" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1305" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1305" t="s">
-        <v>1289</v>
-      </c>
-      <c r="B1305" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1306" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1306" t="s">
-        <v>1310</v>
-      </c>
-      <c r="B1306" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1307" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1307" t="s">
-        <v>1313</v>
-      </c>
-      <c r="B1307" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1308" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1308" t="s">
-        <v>1286</v>
-      </c>
-      <c r="B1308" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1309" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1309" t="s">
-        <v>1283</v>
-      </c>
-      <c r="B1309" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1310" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1310" t="s">
-        <v>1311</v>
-      </c>
-      <c r="B1310" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1311" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1311" t="s">
-        <v>1304</v>
-      </c>
-      <c r="B1311" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1312" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1312" t="s">
-        <v>1285</v>
-      </c>
-      <c r="B1312" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1313" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1313" t="s">
-        <v>1314</v>
-      </c>
-      <c r="B1313" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1314" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1314" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B1314" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1315" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1315" t="s">
-        <v>1292</v>
-      </c>
-      <c r="B1315" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1316" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1316" t="s">
-        <v>1309</v>
-      </c>
-      <c r="B1316" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1317" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1317" t="s">
-        <v>1363</v>
-      </c>
-      <c r="B1317" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1318" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1318" t="s">
-        <v>1337</v>
-      </c>
-      <c r="B1318" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1319" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1319" t="s">
-        <v>1350</v>
-      </c>
-      <c r="B1319" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1320" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1320" t="s">
-        <v>1338</v>
-      </c>
-      <c r="B1320" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1321" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1321" t="s">
-        <v>1333</v>
-      </c>
-      <c r="B1321" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1322" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1322" t="s">
-        <v>1364</v>
-      </c>
-      <c r="B1322" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1323" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1323" t="s">
-        <v>1344</v>
-      </c>
-      <c r="B1323" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1324" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1324" t="s">
-        <v>1320</v>
-      </c>
-      <c r="B1324" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1325" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1325" t="s">
-        <v>1330</v>
-      </c>
-      <c r="B1325" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1326" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1326" t="s">
-        <v>1339</v>
-      </c>
-      <c r="B1326" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1327" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1327" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B1327" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1328" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1328" t="s">
-        <v>1351</v>
-      </c>
-      <c r="B1328" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1329" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1329" t="s">
-        <v>1343</v>
-      </c>
-      <c r="B1329" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1330" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1330" t="s">
-        <v>1358</v>
-      </c>
-      <c r="B1330" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1331" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1331" t="s">
-        <v>1319</v>
-      </c>
-      <c r="B1331" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1332" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1332" t="s">
-        <v>1335</v>
-      </c>
-      <c r="B1332" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1333" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1333" t="s">
-        <v>1336</v>
-      </c>
-      <c r="B1333" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1334" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1334" t="s">
-        <v>1328</v>
-      </c>
-      <c r="B1334" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1335" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1335" t="s">
-        <v>1325</v>
-      </c>
-      <c r="B1335" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1336" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1336" t="s">
-        <v>1360</v>
-      </c>
-      <c r="B1336" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1337" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1337" t="s">
-        <v>1334</v>
-      </c>
-      <c r="B1337" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1338" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1338" t="s">
-        <v>1321</v>
-      </c>
-      <c r="B1338" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1339" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1339" t="s">
-        <v>1341</v>
-      </c>
-      <c r="B1339" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1340" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1340" t="s">
-        <v>1346</v>
-      </c>
-      <c r="B1340" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1341" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1341" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B1341" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1342" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1342" t="s">
-        <v>1327</v>
-      </c>
-      <c r="B1342" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1343" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1343" t="s">
-        <v>1318</v>
-      </c>
-      <c r="B1343" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1344" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1344" t="s">
-        <v>1348</v>
-      </c>
-      <c r="B1344" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1345" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1345" t="s">
-        <v>1345</v>
-      </c>
-      <c r="B1345" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1346" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1346" t="s">
-        <v>1355</v>
-      </c>
-      <c r="B1346" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1347" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1347" t="s">
-        <v>1342</v>
-      </c>
-      <c r="B1347" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1348" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1348" t="s">
-        <v>1324</v>
-      </c>
-      <c r="B1348" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1349" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1349" t="s">
-        <v>1365</v>
-      </c>
-      <c r="B1349" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1350" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1350" t="s">
-        <v>1361</v>
-      </c>
-      <c r="B1350" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1351" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1351" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B1351" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1352" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1352" t="s">
-        <v>1349</v>
-      </c>
-      <c r="B1352" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1353" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1353" t="s">
-        <v>1323</v>
-      </c>
-      <c r="B1353" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1354" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1354" t="s">
-        <v>1354</v>
-      </c>
-      <c r="B1354" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1355" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1355" t="s">
-        <v>1353</v>
-      </c>
-      <c r="B1355" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1356" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1356" t="s">
-        <v>1326</v>
-      </c>
-      <c r="B1356" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1357" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1357" t="s">
-        <v>1322</v>
-      </c>
-      <c r="B1357" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1358" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1358" t="s">
-        <v>1359</v>
-      </c>
-      <c r="B1358" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1359" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1359" t="s">
-        <v>1317</v>
-      </c>
-      <c r="B1359" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1360" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1360" t="s">
-        <v>1347</v>
-      </c>
-      <c r="B1360" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1361" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1361" t="s">
-        <v>1362</v>
-      </c>
-      <c r="B1361" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1362" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1362" t="s">
-        <v>1329</v>
-      </c>
-      <c r="B1362" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1363" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1363" t="s">
-        <v>1352</v>
-      </c>
-      <c r="B1363" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1364" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1364" t="s">
-        <v>1357</v>
-      </c>
-      <c r="B1364" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1365" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1365" t="s">
-        <v>1332</v>
-      </c>
-      <c r="B1365" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1366" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1366" t="s">
-        <v>1340</v>
-      </c>
-      <c r="B1366" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1367" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1367" t="s">
-        <v>1366</v>
-      </c>
-      <c r="B1367" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1368" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1368" t="s">
-        <v>1367</v>
-      </c>
-      <c r="B1368" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1369" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1369" t="s">
-        <v>1368</v>
-      </c>
-      <c r="B1369" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1370" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1370" t="s">
-        <v>1369</v>
-      </c>
-      <c r="B1370" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1371" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1371" t="s">
-        <v>1370</v>
-      </c>
-      <c r="B1371" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1372" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1372" t="s">
-        <v>1371</v>
-      </c>
-      <c r="B1372" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1373" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1373" t="s">
-        <v>1372</v>
-      </c>
-      <c r="B1373" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1374" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1374" t="s">
-        <v>1373</v>
-      </c>
-      <c r="B1374" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1375" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1375" t="s">
-        <v>1374</v>
-      </c>
-      <c r="B1375" t="s">
-        <v>1376</v>
-      </c>
-    </row>
-    <row r="1376" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1376" t="s">
-        <v>1375</v>
-      </c>
-      <c r="B1376" t="s">
-        <v>1376</v>
-      </c>
-    </row>
   </sheetData>
   <sortState ref="C67:C165">
     <sortCondition ref="C67:C165"/>

--- a/train.xlsx
+++ b/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ChatbotPerpusBipa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{675EE7B7-5582-4090-A7CB-DFC3811EAA46}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35E17ED-2982-4CA6-905E-0164EB3A85F5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/train.xlsx
+++ b/train.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ChatbotPerpusBipa\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B35E17ED-2982-4CA6-905E-0164EB3A85F5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6809A54-0C09-4227-AD25-760E3CB50454}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2502" uniqueCount="1253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2978" uniqueCount="1450">
   <si>
     <t>text</t>
   </si>
@@ -3789,6 +3789,597 @@
   </si>
   <si>
     <t>Selamat sore, daftar peraturan yang tidak boleh dilanggar apa saja? Makasih</t>
+  </si>
+  <si>
+    <t>kalau udah nemu bukunya, cara pinjamnya gimana?</t>
+  </si>
+  <si>
+    <t>saya bisa pinjam langsung atau harus isi formulir?</t>
+  </si>
+  <si>
+    <t>pinjam buku perlu minta izin dulu?</t>
+  </si>
+  <si>
+    <t>gimana prosedur kalau mau pinjam buku untuk seminggu?</t>
+  </si>
+  <si>
+    <t>harus daftar dulu ga buat pinjam buku?</t>
+  </si>
+  <si>
+    <t>setelah milih buku, bawa ke mana buat diproses?</t>
+  </si>
+  <si>
+    <t>saya udah punya kartu, tinggal tunjukin aja?</t>
+  </si>
+  <si>
+    <t>ada batas maksimal buku yang bisa dipinjam?</t>
+  </si>
+  <si>
+    <t>kalau pinjam buku digital caranya beda?</t>
+  </si>
+  <si>
+    <t>sistem pinjam sekarang pake barcode atau manual?</t>
+  </si>
+  <si>
+    <t>halo, saya anggota baru belum tau cara pinjam buku di perpus BIPA</t>
+  </si>
+  <si>
+    <t>selamat pagi, kalau cari buku sudah ketemu, langkah pinjamnya apa?</t>
+  </si>
+  <si>
+    <t>maaf, jam layanan untuk pinjam buku sama dengan jam baca di tempat ga?</t>
+  </si>
+  <si>
+    <t>permisi kak, anggota lama ada fasilitas pinjam online ga?</t>
+  </si>
+  <si>
+    <t>halo admin, untuk pinjam buku pakai fasilitas self-service atau manual?</t>
+  </si>
+  <si>
+    <t>selamat sore, peraturan pinjam buku untuk anggota mahasiswa gimana?</t>
+  </si>
+  <si>
+    <t>maaf ganggu, saya udah cari buku yang mau dipinjam tapi bingung prosesnya</t>
+  </si>
+  <si>
+    <t>halo perpus BIPA, cara pinjam buku rujukan berbeda dengan novel ga? terima kasih</t>
+  </si>
+  <si>
+    <t>permisi, anggota senior ada jam khusus untuk pinjam buku ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi, saya mau pinjam tapi takut melanggar peraturan, bisa dijelaskan?</t>
+  </si>
+  <si>
+    <t>ada buku tentang kecerdasan buatan di sini?</t>
+  </si>
+  <si>
+    <t>saya cari novel klasik, ada katalog yang bisa dicek?</t>
+  </si>
+  <si>
+    <t>bisa bantu cariin buku biografi Soekarno?</t>
+  </si>
+  <si>
+    <t>buku hukum internasional edisi 2020 tersedia?</t>
+  </si>
+  <si>
+    <t>saya cari jurnal ekonomi, ada?</t>
+  </si>
+  <si>
+    <t>koleksi komik atau manga juga disediakan?</t>
+  </si>
+  <si>
+    <t>saya mau tau lokasi buku tentang psikologi klinis</t>
+  </si>
+  <si>
+    <t>kalau saya cari buku yang udah dipinjam, bisa ditandai?</t>
+  </si>
+  <si>
+    <t>ada buku-buku referensi untuk skripsi teknik?</t>
+  </si>
+  <si>
+    <t>saya mau cari buku kedokteran yang bisa dibaca di tempat</t>
+  </si>
+  <si>
+    <t>halo, perpus BIPA punya koleksi buku anggota yang lengkap ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi, saya mau cek jam layanan untuk cari buku sejarah</t>
+  </si>
+  <si>
+    <t>maaf, untuk anggota ada fasilitas booking buku yang sedang dipinjam?</t>
+  </si>
+  <si>
+    <t>permisi kak, saya cari buku tapi ga tau caranya pinjam, bisa dibantu?</t>
+  </si>
+  <si>
+    <t>halo admin, koleksi buku digital jam aksesnya sama dengan jam perpus ga?</t>
+  </si>
+  <si>
+    <t>selamat sore, ada ga buku tentang peraturan perpustakaan modern?</t>
+  </si>
+  <si>
+    <t>maaf ganggu, saya anggota baru mau tau cara cari buku paling efektif</t>
+  </si>
+  <si>
+    <t>halo perpus BIPA, katalog online bisa diakses anggota 24 jam? terima kasih</t>
+  </si>
+  <si>
+    <t>permisi, buku yang lagi dipinjam anggota lain bisa direservasi ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi, saya cari buku tentang manajemen jam kerja, ada ga?</t>
+  </si>
+  <si>
+    <t>apakah ada komputer umum di perpus?</t>
+  </si>
+  <si>
+    <t>ada ruang rapat kecil untuk belajar kelompok?</t>
+  </si>
+  <si>
+    <t>perpus nyediain loker penyimpanan barang?</t>
+  </si>
+  <si>
+    <t>saya bisa nge-print atau fotokopi dari sini?</t>
+  </si>
+  <si>
+    <t>ruang baca di lantai atas bebas dipakai siapa aja?</t>
+  </si>
+  <si>
+    <t>bisa pakai colokan listrik buat laptop?</t>
+  </si>
+  <si>
+    <t>ada akses wifi buat pengunjung umum?</t>
+  </si>
+  <si>
+    <t>ada tempat untuk baca sambil diskusi pelan-pelan?</t>
+  </si>
+  <si>
+    <t>tempat duduk yang di pojok itu bisa dipakai mahasiswa?</t>
+  </si>
+  <si>
+    <t>ruang multimedia-nya aktif sekarang?</t>
+  </si>
+  <si>
+    <t>halo, anggota bisa pinjam fasilitas ruang meeting ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi, jam layanan komputer umum sama dengan jam perpus?</t>
+  </si>
+  <si>
+    <t>maaf, untuk cari buku pakai komputer katalog atau tanya petugas?</t>
+  </si>
+  <si>
+    <t>permisi kak, fasilitas fotokopi ada peraturan khusus ga?</t>
+  </si>
+  <si>
+    <t>halo admin, saya anggota mau tau cara pinjam ruang diskusi</t>
+  </si>
+  <si>
+    <t>selamat sore, wifi perpus BIPA bisa diakses tanpa jadi anggota?</t>
+  </si>
+  <si>
+    <t>maaf ganggu, ruang baca ada jam khusus atau mengikuti jam layanan perpus?</t>
+  </si>
+  <si>
+    <t>halo, fasilitas loker bisa dipinjam berapa lama? terima kasih</t>
+  </si>
+  <si>
+    <t>permisi, anggota dapat prioritas untuk pakai fasilitas komputer ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi, saya mau cari buku tapi sekalian butuh akses internet, bisa ga?</t>
+  </si>
+  <si>
+    <t>kalau saya datang hari minggu, perpustakaan buka ga?</t>
+  </si>
+  <si>
+    <t>saya bisa ke perpustakaan jam 7 malam?</t>
+  </si>
+  <si>
+    <t>apakah boleh masuk perpus jam istirahat siang?</t>
+  </si>
+  <si>
+    <t>kapan terakhir pengunjung bisa masuk?</t>
+  </si>
+  <si>
+    <t>saya mau datang tanggal merah, masih bisa?</t>
+  </si>
+  <si>
+    <t>buka sampai jam berapa kalau hari Jumat?</t>
+  </si>
+  <si>
+    <t>saya datang sore, masih bisa pinjam buku ga?</t>
+  </si>
+  <si>
+    <t>saya pengen ke perpus malam ini, masih dilayani?</t>
+  </si>
+  <si>
+    <t>kalau long weekend gini, perpus buka atau tutup?</t>
+  </si>
+  <si>
+    <t>saya bisa datang setelah kuliah jam 4 sore?</t>
+  </si>
+  <si>
+    <t>halo, perpus BIPA buka jam berapa ya hari sabtu?</t>
+  </si>
+  <si>
+    <t>selamat pagi, jadwal layanan perpustakaan BIPA gimana?</t>
+  </si>
+  <si>
+    <t>maaf mau tanya, kalau libur nasional perpus tutup ya?</t>
+  </si>
+  <si>
+    <t>siang kak, perpus masih buka jam 9 malam ga? terima kasih</t>
+  </si>
+  <si>
+    <t>halo admin, saya anggota baru mau tanya jam operasional</t>
+  </si>
+  <si>
+    <t>permisi, untuk hari kerja perpus BIPA tutup jam berapa?</t>
+  </si>
+  <si>
+    <t>maaf ganggu, kalau ramadan jam buka berubah ga?</t>
+  </si>
+  <si>
+    <t>selamat sore, saya mau ke perpus tapi takut udah tutup</t>
+  </si>
+  <si>
+    <t>saya bukan mahasiswa sini, boleh masuk perpus?</t>
+  </si>
+  <si>
+    <t>kalo ga punya kartu anggota, boleh pinjam buku?</t>
+  </si>
+  <si>
+    <t>saya baru pindahan, bisa daftar jadi anggota?</t>
+  </si>
+  <si>
+    <t>gimana caranya kalau saya mau jadi anggota perpus?</t>
+  </si>
+  <si>
+    <t>saya kehilangan kartu, masih bisa masuk?</t>
+  </si>
+  <si>
+    <t>jadi anggota bayar atau gratis?</t>
+  </si>
+  <si>
+    <t>saya anak SMA, bisa daftar jadi anggota?</t>
+  </si>
+  <si>
+    <t>saya udah daftar tapi belum punya kartu, bisa dipakai?</t>
+  </si>
+  <si>
+    <t>anggota perpus dapat akses semua buku ya?</t>
+  </si>
+  <si>
+    <t>anggota bisa bawa laptop sendiri ke ruang baca?</t>
+  </si>
+  <si>
+    <t>apakah mahasiswa boleh meminjam buku walau bukan anggota?</t>
+  </si>
+  <si>
+    <t>halo, saya guru SD mau daftar anggota perpus BIPA bisa ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi, syarat jadi anggota perpustakaan apa aja ya?</t>
+  </si>
+  <si>
+    <t>maaf, kartu saya hilang tapi saya anggota lama, gimana caranya?</t>
+  </si>
+  <si>
+    <t>permisi kak, untuk fasilitas wifi perlu jadi anggota dulu ga?</t>
+  </si>
+  <si>
+    <t>halo admin, anggota bisa akses jam layanan yang berbeda ga?</t>
+  </si>
+  <si>
+    <t>saya pensiunan mau cari buku, perlu daftar anggota atau langsung bisa?</t>
+  </si>
+  <si>
+    <t>selamat sore, anak saya umur 15 tahun bisa bikin kartu anggota sendiri? terima kasih</t>
+  </si>
+  <si>
+    <t>maaf mau tanya, kalau sudah anggota tapi pindah alamat gimana updatenya?</t>
+  </si>
+  <si>
+    <t>halo perpus BIPA, saya dosen tamu di kampus ini, bisa jadi anggota temporer ga?</t>
+  </si>
+  <si>
+    <t>boleh bawa makanan ringan ke ruang baca?</t>
+  </si>
+  <si>
+    <t>saya harus diam di ruang baca ya?</t>
+  </si>
+  <si>
+    <t>kalau telat balikin buku, dendanya berapa?</t>
+  </si>
+  <si>
+    <t>boleh ngajak teman diskusi pelan di ruang baca?</t>
+  </si>
+  <si>
+    <t>apa semua pengunjung harus isi buku tamu?</t>
+  </si>
+  <si>
+    <t>ada aturan soal pakaian di perpus?</t>
+  </si>
+  <si>
+    <t>boleh telepon di dalam perpustakaan?</t>
+  </si>
+  <si>
+    <t>peraturan untuk bawa kamera ke dalam gimana?</t>
+  </si>
+  <si>
+    <t>harus scan kartu setiap masuk ya?</t>
+  </si>
+  <si>
+    <t>kalau ketahuan merusak buku, kena sanksi apa?</t>
+  </si>
+  <si>
+    <t>halo, ada peraturan khusus untuk anggota yang sering pinjam buku ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi, peraturan jam masuk perpus BIPA berlaku untuk semua anggota?</t>
+  </si>
+  <si>
+    <t>maaf, kalau saya cari buku sambil makan boleh ga?</t>
+  </si>
+  <si>
+    <t>permisi kak, ada aturan pakai fasilitas wifi ga?</t>
+  </si>
+  <si>
+    <t>halo admin, peraturan untuk anggota yang telat bayar denda gimana?</t>
+  </si>
+  <si>
+    <t>selamat sore, saya anggota baru mau tau peraturan jam layanan weekday</t>
+  </si>
+  <si>
+    <t>maaf ganggu, aturan pinjam buku untuk mahasiswa sama dengan umum ga?</t>
+  </si>
+  <si>
+    <t>halo perpus BIPA, peraturan pakai fasilitas komputer ada batasan waktu? terima kasih</t>
+  </si>
+  <si>
+    <t>permisi, ada sanksi kalau anggota melanggar jam operasional ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi, peraturan untuk cari buku di area terlarang gimana ya?</t>
+  </si>
+  <si>
+    <t>kalau udah nemu bukunya cara pinjamnya gimana?</t>
+  </si>
+  <si>
+    <t>setelah milih buku bawa ke mana buat diproses?</t>
+  </si>
+  <si>
+    <t>saya udah punya kartu tinggal tunjukin aja?</t>
+  </si>
+  <si>
+    <t>halo kak mau tanya cara perpanjang pinjaman buku gimana?</t>
+  </si>
+  <si>
+    <t>selamat pagi prosedur pengembalian buku yang terlambat bagaimana?</t>
+  </si>
+  <si>
+    <t>permisi bisa pinjam buku tanpa kartu anggota ga?</t>
+  </si>
+  <si>
+    <t>hai admin durasi peminjaman buku maksimal berapa lama?</t>
+  </si>
+  <si>
+    <t>maaf mau nanya bisa pinjam buku lewat online tidak?</t>
+  </si>
+  <si>
+    <t>excuse me kalau mau booking buku caranya gimana?</t>
+  </si>
+  <si>
+    <t>selamat sore bisa pinjam lebih dari 3 buku sekaligus ga?</t>
+  </si>
+  <si>
+    <t>halo kak cara cek status peminjaman buku bagaimana?</t>
+  </si>
+  <si>
+    <t>mau tanya dong prosedur pinjam buku referensi gimana terima kasih</t>
+  </si>
+  <si>
+    <t>siang kak tolong jelaskan step by step cara pinjam buku dong makasih</t>
+  </si>
+  <si>
+    <t>saya cari novel klasik ada katalog yang bisa dicek?</t>
+  </si>
+  <si>
+    <t>saya cari jurnal ekonomi ada?</t>
+  </si>
+  <si>
+    <t>kalau saya cari buku yang udah dipinjam bisa ditandai?</t>
+  </si>
+  <si>
+    <t>halo kak ada koleksi buku sejarah Indonesia ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi mau cari buku tentang machine learning ada tidak?</t>
+  </si>
+  <si>
+    <t>permisi bisa bantu carikan buku statistik untuk penelitian?</t>
+  </si>
+  <si>
+    <t>hai admin ada buku novel terbaru karya penulis Indonesia?</t>
+  </si>
+  <si>
+    <t>maaf mau nanya ada koleksi thesis dan disertasi ga?</t>
+  </si>
+  <si>
+    <t>excuse me buku-buku bahasa Inggris ada di lantai berapa?</t>
+  </si>
+  <si>
+    <t>selamat sore ada buku tentang entrepreneurship tidak ya?</t>
+  </si>
+  <si>
+    <t>halo kak koleksi buku agama lengkap ga di sini?</t>
+  </si>
+  <si>
+    <t>mau tanya dong ada buku komputasi awan ga terima kasih</t>
+  </si>
+  <si>
+    <t>siang kak tolong carikan buku tentang leadership dong makasih</t>
+  </si>
+  <si>
+    <t>halo kak ada fasilitas AC di ruang baca ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi mau tanya ada mushola di perpustakaan tidak?</t>
+  </si>
+  <si>
+    <t>permisi fasilitas toilet ada di lantai berapa ya?</t>
+  </si>
+  <si>
+    <t>hai admin ada tempat parkir khusus untuk pengunjung perpus?</t>
+  </si>
+  <si>
+    <t>maaf mau nanya ada kantin atau cafe di dalam perpustakaan?</t>
+  </si>
+  <si>
+    <t>excuse me ada ruang santai atau area istirahat ga?</t>
+  </si>
+  <si>
+    <t>selamat sore ada fasilitas scanner untuk dokumen tidak?</t>
+  </si>
+  <si>
+    <t>halo kak ruang diskusi bisa dibooking ga?</t>
+  </si>
+  <si>
+    <t>mau tanya dong ada lift untuk ke lantai atas terima kasih</t>
+  </si>
+  <si>
+    <t>siang kak info fasilitas yang tersedia di perpus dong makasih</t>
+  </si>
+  <si>
+    <t>kalau saya datang hari minggu perpustakaan buka ga?</t>
+  </si>
+  <si>
+    <t>saya mau datang tanggal merah masih bisa?</t>
+  </si>
+  <si>
+    <t>saya datang sore masih bisa pinjam buku ga?</t>
+  </si>
+  <si>
+    <t>saya pengen ke perpus malam ini masih dilayani?</t>
+  </si>
+  <si>
+    <t>kalau long weekend gini perpus buka atau tutup?</t>
+  </si>
+  <si>
+    <t>halo kak mau tanya perpus hari libur buka tidak?</t>
+  </si>
+  <si>
+    <t>selamat pagi bisa tanya jam operasional perpustakaan?</t>
+  </si>
+  <si>
+    <t>permisi mau tanya perpus tutup jam berapa ya?</t>
+  </si>
+  <si>
+    <t>excuse me perpustakaan weekend buka ga kak?</t>
+  </si>
+  <si>
+    <t>maaf mau nanya perpus sabtu minggu tetap buka?</t>
+  </si>
+  <si>
+    <t>hai kak perpus bulan puasa jam berapa tutupnya?</t>
+  </si>
+  <si>
+    <t>selamat siang perpustakaan hari raya buka tidak ya?</t>
+  </si>
+  <si>
+    <t>halo admin jam buka perpus hari ini sampai jam berapa?</t>
+  </si>
+  <si>
+    <t>mau tanya dong perpus malam masih buka ga terima kasih</t>
+  </si>
+  <si>
+    <t>siang kak info jam layanan perpustakaan dong makasih</t>
+  </si>
+  <si>
+    <t>saya bukan mahasiswa sini boleh masuk perpus?</t>
+  </si>
+  <si>
+    <t>kalo ga punya kartu anggota boleh pinjam buku?</t>
+  </si>
+  <si>
+    <t>saya baru pindahan bisa daftar jadi anggota?</t>
+  </si>
+  <si>
+    <t>saya kehilangan kartu masih bisa masuk?</t>
+  </si>
+  <si>
+    <t>saya anak SMA bisa daftar jadi anggota?</t>
+  </si>
+  <si>
+    <t>saya udah daftar tapi belum punya kartu bisa dipakai?</t>
+  </si>
+  <si>
+    <t>halo kak saya mahasiswa luar daerah bisa jadi member ga?</t>
+  </si>
+  <si>
+    <t>selamat pagi mau daftar anggota perpustakaan caranya gimana?</t>
+  </si>
+  <si>
+    <t>permisi mau tanya syarat jadi anggota perpus apa aja?</t>
+  </si>
+  <si>
+    <t>hai admin bisa bantu info cara perpanjang keanggotaan?</t>
+  </si>
+  <si>
+    <t>maaf mau nanya kalau bukan sivitas akademika boleh daftar tidak?</t>
+  </si>
+  <si>
+    <t>excuse me saya guru bisa jadi anggota perpustakaan ga?</t>
+  </si>
+  <si>
+    <t>selamat sore persyaratan daftar anggota perpus apa ya?</t>
+  </si>
+  <si>
+    <t>halo kak kartu anggota saya rusak bisa diganti tidak?</t>
+  </si>
+  <si>
+    <t>mau tanya dong biaya keanggotaan perpus berapa ya terima kasih</t>
+  </si>
+  <si>
+    <t>siang kak info keanggotaan perpustakaan untuk umum dong makasih</t>
+  </si>
+  <si>
+    <t>kalau telat balikin buku dendanya berapa?</t>
+  </si>
+  <si>
+    <t>kalau ketahuan merusak buku kena sanksi apa?</t>
+  </si>
+  <si>
+    <t>halo kak mau tanya peraturan jam malam di perpustakaan gimana?</t>
+  </si>
+  <si>
+    <t>selamat pagi boleh bawa tas besar ke ruang baca tidak?</t>
+  </si>
+  <si>
+    <t>permisi aturan untuk mahasiswa asing sama ga dengan lokal?</t>
+  </si>
+  <si>
+    <t>hai admin boleh tidur di ruang baca kalau capek?</t>
+  </si>
+  <si>
+    <t>maaf mau nanya dress code masuk perpustakaan ada ga?</t>
+  </si>
+  <si>
+    <t>excuse me boleh charge hp di ruang baca ga?</t>
+  </si>
+  <si>
+    <t>selamat sore ada larangan khusus untuk anak-anak tidak?</t>
+  </si>
+  <si>
+    <t>halo kak peraturan penggunaan laptop di perpus bagaimana?</t>
+  </si>
+  <si>
+    <t>mau tanya dong denda keterlambatan per hari berapa ya terima kasih</t>
+  </si>
+  <si>
+    <t>siang kak tolong info tata tertib lengkap perpustakaan dong makasih</t>
   </si>
 </sst>
 </file>
@@ -4635,7 +5226,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C1251"/>
+  <dimension ref="A1:C1489"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="100.28515625" bestFit="1" customWidth="1"/>
@@ -14658,6 +15249,1910 @@
         <v>1127</v>
       </c>
     </row>
+    <row r="1252" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1252" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B1252" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1253" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B1253" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1254" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B1254" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1255" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1256" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B1256" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1257" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B1257" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1258" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B1258" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1259" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1260" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1261" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1262" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1263" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1264" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B1264" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1265" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B1265" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1266" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1267" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1268" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1269" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1270" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B1270" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1271" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1272" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B1272" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1273" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1274" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B1274" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1275" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B1275" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1276" t="s">
+        <v>1277</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1277" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1278" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1279" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1279" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B1279" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1280" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1280" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B1280" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1281" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1281" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B1281" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1282" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1282" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B1282" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1283" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1283" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B1283" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1284" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1284" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B1284" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1285" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1285" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B1285" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1286" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1286" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B1286" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1287" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1287" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1288" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1288" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B1288" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1289" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1289" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B1289" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1290" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1290" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B1290" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1291" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1291" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B1291" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1292" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1292" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B1292" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1293" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1293" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B1293" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1294" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1294" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B1294" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1295" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1295" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B1295" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1296" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1296" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B1296" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1297" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1297" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B1297" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1298" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1298" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B1298" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1299" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1299" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B1299" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1300" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1300" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B1300" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1301" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1301" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B1301" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1302" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1302" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B1302" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1303" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1303" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B1303" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1304" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1304" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B1304" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1305" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1305" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B1305" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1306" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1306" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B1306" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1307" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1307" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B1307" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1308" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1308" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B1308" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1309" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1309" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B1309" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1310" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1310" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B1310" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1311" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1311" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B1311" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1312" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1312" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B1312" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1313" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1313" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B1313" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1314" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1314" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1314" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1315" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1315" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B1315" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1316" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1316" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B1316" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1317" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1317" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B1317" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1318" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1318" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B1318" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1319" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1319" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B1319" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1320" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1320" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B1320" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1321" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1321" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B1321" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1322" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1322" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B1322" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1323" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1323" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B1323" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1324" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1324" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B1324" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1325" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1325" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B1325" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1326" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1326" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B1326" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1327" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1327" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B1327" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1328" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1328" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B1328" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1329" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1329" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B1329" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1330" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1330" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B1330" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1331" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1331" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B1331" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1332" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1332" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B1332" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1333" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1333" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B1333" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1334" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1334" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B1334" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1335" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1335" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B1335" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1336" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1336" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B1336" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1337" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1337" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B1337" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1338" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1338" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B1338" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1339" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1339" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B1339" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1340" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1340" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B1340" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1341" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1341" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B1341" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1342" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1342" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B1342" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1343" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1343" t="s">
+        <v>1344</v>
+      </c>
+      <c r="B1343" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1344" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1344" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B1344" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1345" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1345" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B1345" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1346" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1346" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B1346" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1347" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1347" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B1347" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1348" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1348" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B1348" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1349" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1349" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B1349" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1350" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1350" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B1350" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1351" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1351" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B1351" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1352" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1352" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B1352" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1353" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1353" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1353" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1354" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1354" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B1354" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1355" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1355" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B1355" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1356" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1356" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B1356" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1357" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1357" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B1357" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1358" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1358" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B1358" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1359" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1359" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B1359" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1360" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1360" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1360" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1361" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1361" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B1361" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1362" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1362" t="s">
+        <v>1363</v>
+      </c>
+      <c r="B1362" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1363" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1363" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B1363" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1364" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1364" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B1364" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1365" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1365" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B1365" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1366" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1366" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B1366" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1367" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1367" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B1367" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1368" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1368" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B1368" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1369" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1369" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1369" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1370" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1370" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B1370" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1371" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1371" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B1371" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1372" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1372" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B1372" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1373" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1373" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B1373" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1374" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1374" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B1374" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1375" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1375" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B1375" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1376" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1376" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B1376" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1377" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1377" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B1377" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1378" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1378" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B1378" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1379" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1379" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B1379" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1380" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1380" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B1380" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1381" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1381" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B1381" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1382" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1382" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B1382" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1383" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1383" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B1383" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1384" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1384" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B1384" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1385" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1385" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B1385" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1386" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1386" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B1386" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1387" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1387" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B1387" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1388" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1388" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B1388" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1389" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1389" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B1389" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="1390" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1390" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B1390" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1391" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1391" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B1391" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1392" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1392" t="s">
+        <v>1275</v>
+      </c>
+      <c r="B1392" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1393" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1393" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B1393" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1394" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1394" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B1394" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1395" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1395" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B1395" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1396" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1396" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B1396" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1397" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1397" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B1397" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1398" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1398" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B1398" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1399" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1399" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B1399" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1400" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1400" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B1400" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1401" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1401" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B1401" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1402" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1402" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B1402" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1403" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1403" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B1403" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1404" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1404" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B1404" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1405" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1405" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B1405" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1406" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1406" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B1406" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1407" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1407" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B1407" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1408" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1408" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B1408" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1409" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1409" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B1409" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="1410" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1410" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B1410" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1411" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1411" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B1411" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1412" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1412" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B1412" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1413" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1413" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B1413" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1414" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1414" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B1414" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1415" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1415" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B1415" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1416" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1416" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B1416" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1417" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1417" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B1417" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1418" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1418" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B1418" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1419" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1419" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B1419" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1420" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1420" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B1420" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1421" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1421" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B1421" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1422" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1422" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B1422" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1423" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1423" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B1423" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1424" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1424" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B1424" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1425" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1425" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B1425" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1426" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1426" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B1426" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1427" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1427" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B1427" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1428" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1428" t="s">
+        <v>1405</v>
+      </c>
+      <c r="B1428" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1429" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1429" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B1429" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="1430" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1430" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B1430" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1431" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1431" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B1431" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1432" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1432" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B1432" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1433" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1433" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B1433" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1434" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1434" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B1434" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1435" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1435" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B1435" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1436" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1436" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B1436" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1437" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1437" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B1437" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1438" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1438" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B1438" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1439" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1439" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B1439" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1440" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1440" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B1440" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1441" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1441" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B1441" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1442" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1442" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B1442" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1443" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1443" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B1443" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1444" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1444" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B1444" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1445" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1445" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B1445" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1446" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1446" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B1446" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1447" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1447" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B1447" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1448" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1448" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B1448" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1449" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1449" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B1449" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="1450" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1450" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B1450" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1451" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1451" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B1451" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1452" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1452" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B1452" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1453" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1453" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B1453" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1454" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1454" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B1454" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1455" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1455" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B1455" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1456" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1456" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B1456" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1457" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1457" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B1457" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1458" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1458" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B1458" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1459" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1459" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B1459" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1460" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1461" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1462" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1463" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1464" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1465" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1466" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1467" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1468" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1469" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1470" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1471" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1472" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1473" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1474" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1475" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1476" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1477" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1478" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1479" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1480" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1481" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1482" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1483" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1484" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1485" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1486" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1487" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1488" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1489" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>1127</v>
+      </c>
+    </row>
   </sheetData>
   <sortState ref="C67:C165">
     <sortCondition ref="C67:C165"/>
